--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-FRM-43_lpa_kontrol_ve_karsi_onlem_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-FRM-43_lpa_kontrol_ve_karsi_onlem_formu.xlsx
@@ -934,7 +934,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-43&amp;C&amp;"Arial,Regular"&amp;11LPA Kontrol ve Karşı Önlem Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: U/UD/NA sonuçları ve denetim tamamlık kontrolü eklendi; gerçek lojistik koşullarına göre sorular sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1068,7 +1069,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-43&amp;C&amp;"Arial,Regular"&amp;11LPA Kontrol ve Karşı Önlem Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: U/UD/NA sonuçları ve denetim tamamlık kontrolü eklendi; gerçek lojistik koşullarına göre sorular sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>